--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="357">
   <si>
     <t/>
   </si>
@@ -550,6 +550,12 @@
     <t>BIHUN JAGUNG 320G</t>
   </si>
   <si>
+    <t>10037027</t>
+  </si>
+  <si>
+    <t>AAA BIHUN 220GR</t>
+  </si>
+  <si>
     <t>20140909</t>
   </si>
   <si>
@@ -649,6 +655,12 @@
     <t>WNHAE FRIED ROSE 97G</t>
   </si>
   <si>
+    <t>20141816</t>
+  </si>
+  <si>
+    <t>N/SHIM TOOMBA 137GR</t>
+  </si>
+  <si>
     <t>20117989</t>
   </si>
   <si>
@@ -809,12 +821,6 @@
   </si>
   <si>
     <t>SP.BHUN INST KUAH 51</t>
-  </si>
-  <si>
-    <t>10037027</t>
-  </si>
-  <si>
-    <t>AAA BIHUN 220GR</t>
   </si>
   <si>
     <t>20039011</t>
@@ -1468,7 +1474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F160"/>
+  <dimension ref="A1:F161"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2973,7 +2979,7 @@
         <v>166</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>19</v>
@@ -2993,7 +2999,7 @@
         <v>166</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>169</v>
@@ -3013,7 +3019,7 @@
         <v>166</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>6</v>
@@ -3033,7 +3039,7 @@
         <v>166</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>6</v>
@@ -3053,7 +3059,7 @@
         <v>166</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>176</v>
@@ -3073,7 +3079,7 @@
         <v>166</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>6</v>
@@ -3090,53 +3096,53 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="E82" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>184</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3150,53 +3156,53 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="E85" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>192</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3210,13 +3216,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3230,13 +3236,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3250,13 +3256,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3270,13 +3276,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3290,10 +3296,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>19</v>
@@ -3301,19 +3307,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>19</v>
@@ -3330,10 +3336,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>19</v>
@@ -3350,13 +3356,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3370,13 +3376,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3390,13 +3396,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>169</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3410,10 +3416,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>19</v>
@@ -3421,39 +3427,39 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>19</v>
@@ -3470,10 +3476,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>19</v>
@@ -3490,10 +3496,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>19</v>
@@ -3510,10 +3516,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>19</v>
@@ -3521,19 +3527,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>19</v>
@@ -3541,22 +3547,22 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3570,13 +3576,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3590,13 +3596,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3610,13 +3616,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3630,10 +3636,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>19</v>
@@ -3641,19 +3647,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>19</v>
@@ -3661,19 +3667,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>19</v>
@@ -3690,10 +3696,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>19</v>
@@ -3710,10 +3716,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -3730,10 +3736,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>19</v>
@@ -3750,10 +3756,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>19</v>
@@ -3770,10 +3776,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>19</v>
@@ -3781,19 +3787,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>19</v>
@@ -3801,19 +3807,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
@@ -3830,10 +3836,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>19</v>
@@ -3850,13 +3856,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3870,13 +3876,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>169</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3890,10 +3896,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>6</v>
@@ -3901,22 +3907,22 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3930,10 +3936,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>169</v>
@@ -3950,13 +3956,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3970,13 +3976,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3990,10 +3996,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>19</v>
@@ -4010,10 +4016,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>19</v>
@@ -4030,10 +4036,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>19</v>
@@ -4041,19 +4047,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>19</v>
@@ -4070,10 +4076,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>19</v>
@@ -4090,10 +4096,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>19</v>
@@ -4110,10 +4116,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>19</v>
@@ -4130,13 +4136,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>169</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4150,10 +4156,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>169</v>
@@ -4170,10 +4176,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>169</v>
@@ -4190,30 +4196,30 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>19</v>
@@ -4230,10 +4236,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>19</v>
@@ -4250,10 +4256,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>19</v>
@@ -4270,30 +4276,30 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4310,10 +4316,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4330,10 +4336,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4350,10 +4356,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4370,10 +4376,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4390,10 +4396,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4410,10 +4416,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4421,19 +4427,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4450,10 +4456,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4470,10 +4476,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4490,10 +4496,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4510,10 +4516,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4521,19 +4527,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="C153" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C153" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E153" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4550,10 +4556,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>6</v>
@@ -4570,10 +4576,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>6</v>
@@ -4590,33 +4596,33 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>192</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="E157" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4630,13 +4636,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4650,13 +4656,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4670,12 +4676,32 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F160" s="1" t="s">
+      <c r="F161" s="1" t="s">
         <v>19</v>
       </c>
     </row>
